--- a/data/file_generation/reference/data_219/端侧订单记录_已清洗_res.xlsx
+++ b/data/file_generation/reference/data_219/端侧订单记录_已清洗_res.xlsx
@@ -905,18 +905,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8BD64C-0A4C-44FD-8DCF-640FCAEFEF99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11FB0C86-D540-4E80-A6BD-3E5E3CB0FAC2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF38B68F-932D-4068-878E-2AB31FA4C5BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95ADF4DC-0000-484F-B34A-18C05FD66293}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B20109A2-93FC-449E-8CF8-E950AE3B1FAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D268120C-6CB1-4D3D-B7BA-744B323DE5C6}"/>
 </file>